--- a/download/Топольное_тест/BoQ_FTTH_Топольное_тест_генерализации.xlsx
+++ b/download/Топольное_тест/BoQ_FTTH_Топольное_тест_генерализации.xlsx
@@ -588,7 +588,7 @@
     <row r="3" ht="14" customHeight="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Сеть спроектирована по спутниковым снимкам с привязкой к дорогам OSM • допущения — лист «Методика» • подготовлено 23.09.2026</t>
+          <t>Сеть спроектирована по спутниковым снимкам с привязкой к дорогам OSM • допущения — лист «Методика» • подготовлено 24.09.2026</t>
         </is>
       </c>
     </row>
@@ -737,7 +737,7 @@
         </is>
       </c>
       <c r="F9" s="11" t="n">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="G9" s="12">
         <f>SUM(F9:F9)</f>
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G12" s="14">
         <f>SUM(F12:F12)</f>
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="F13" s="15" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="G13" s="16">
         <f>SUM(F13:F13)</f>
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="G14" s="14">
         <f>SUM(F14:F14)</f>
@@ -884,7 +884,7 @@
         </is>
       </c>
       <c r="F15" s="15" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="G15" s="16">
         <f>SUM(F15:F15)</f>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="G16" s="14">
         <f>SUM(F16:F16)</f>
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="F17" s="15" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="G17" s="16">
         <f>SUM(F17:F17)</f>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="F21" s="15" t="n">
-        <v>12</v>
+        <v>12.2</v>
       </c>
       <c r="G21" s="16">
         <f>SUM(F21:F21)</f>
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>245.2</v>
+        <v>248</v>
       </c>
       <c r="G22" s="14">
         <f>SUM(F22:F22)</f>
@@ -1112,7 +1112,7 @@
         </is>
       </c>
       <c r="F24" s="7" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G24" s="8">
         <f>SUM(F24:F24)</f>
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="F26" s="7" t="n">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="G26" s="8">
         <f>SUM(F26:F26)</f>
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="F27" s="11" t="n">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="G27" s="12">
         <f>SUM(F27:F27)</f>
@@ -1205,7 +1205,7 @@
         </is>
       </c>
       <c r="F28" s="7" t="n">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="G28" s="8">
         <f>SUM(F28:F28)</f>
@@ -1232,7 +1232,7 @@
         </is>
       </c>
       <c r="F29" s="11" t="n">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="G29" s="12">
         <f>SUM(F29:F29)</f>
@@ -1286,7 +1286,7 @@
         </is>
       </c>
       <c r="F31" s="11" t="n">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="G31" s="12">
         <f>SUM(F31:F31)</f>
@@ -1313,7 +1313,7 @@
         </is>
       </c>
       <c r="F32" s="7" t="n">
-        <v>1530</v>
+        <v>1548</v>
       </c>
       <c r="G32" s="8">
         <f>SUM(F32:F32)</f>
@@ -1392,7 +1392,7 @@
     <row r="3" ht="14" customHeight="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>ДХ — домохозяйства. «Верхний участок» — максимум волокон на участке; «маршрут волокна» — от обслуживающего ОРШ зоны до муфты ДХ. Подготовлено 23.09.2026</t>
+          <t>ДХ — домохозяйства. «Верхний участок» — максимум волокон на участке; «маршрут волокна» — от обслуживающего ОРШ зоны до муфты ДХ. Подготовлено 24.09.2026</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E5" s="17" t="n"/>
       <c r="F5" s="7" t="n">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="G5" s="7">
         <f>IFERROR(F5/E5-1,"")</f>
@@ -1511,34 +1511,34 @@
         <v>3</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J5" s="7" t="n">
         <v>14.03</v>
       </c>
       <c r="K5" s="19" t="n">
-        <v>11.38</v>
+        <v>11.52</v>
       </c>
       <c r="L5" s="19" t="n">
-        <v>44.6</v>
+        <v>44.7</v>
       </c>
       <c r="M5" s="7" t="n">
         <v>98.8</v>
       </c>
       <c r="N5" s="7" t="n">
-        <v>245.2</v>
+        <v>248</v>
       </c>
       <c r="O5" s="7" t="n">
-        <v>429</v>
+        <v>432.4</v>
       </c>
       <c r="P5" s="7" t="n">
         <v>6</v>
       </c>
       <c r="Q5" s="7" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="R5" s="7" t="n">
-        <v>539.3</v>
+        <v>543.4</v>
       </c>
     </row>
     <row r="6" ht="26" customHeight="1">
@@ -1642,7 +1642,7 @@
     <row r="3" ht="14" customHeight="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Топология сетей, муфты и дропы в обеих схемах одинаковы — различается размещение сплиттеров и формирование ёмкостей. Подготовлено 23.09.2026</t>
+          <t>Топология сетей, муфты и дропы в обеих схемах одинаковы — различается размещение сплиттеров и формирование ёмкостей. Подготовлено 24.09.2026</t>
         </is>
       </c>
     </row>
@@ -1675,10 +1675,10 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="E5" s="25">
         <f>IFERROR(D5/C5-1,"")</f>
@@ -1709,10 +1709,10 @@
         </is>
       </c>
       <c r="C7" s="13" t="n">
-        <v>429</v>
+        <v>432.4</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>245.2</v>
+        <v>248</v>
       </c>
       <c r="E7" s="13">
         <f>IFERROR(D7/C7-1,"")</f>
@@ -1743,10 +1743,10 @@
         </is>
       </c>
       <c r="C9" s="13" t="n">
-        <v>12</v>
+        <v>12.2</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>12</v>
+        <v>12.2</v>
       </c>
       <c r="E9" s="13">
         <f>IFERROR(D9/C9-1,"")</f>
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="C10" s="15" t="n">
-        <v>28.5</v>
+        <v>28.7</v>
       </c>
       <c r="D10" s="15" t="n">
-        <v>27.4</v>
+        <v>27.6</v>
       </c>
       <c r="E10" s="15">
         <f>IFERROR(D10/C10-1,"")</f>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="C11" s="7" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E11" s="25">
         <f>IFERROR(D11/C11-1,"")</f>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D12" s="11" t="n">
         <v>6</v>
@@ -1811,10 +1811,10 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>561</v>
+        <v>568</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="E13" s="25">
         <f>IFERROR(D13/C13-1,"")</f>
@@ -1880,7 +1880,7 @@
     <row r="3" ht="14" customHeight="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Расчёт выполнен по геометрии спроектированных сетей (ЦУ → зонные ОРШ → муфты → ДХ). Подготовлено 23.09.2026</t>
+          <t>Расчёт выполнен по геометрии спроектированных сетей (ЦУ → зонные ОРШ → муфты → ДХ). Подготовлено 24.09.2026</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="D8" s="28" t="inlineStr">
         <is>
-          <t>255 ДХ. Отклонения от данных заказа связаны с покрытием дорог OSM и фактической застройкой; при больших расхождениях проверьте домохозяйства по превью стадии households.</t>
+          <t>258 ДХ. Отклонения от данных заказа связаны с покрытием дорог OSM и фактической застройкой; при больших расхождениях проверьте домохозяйства по превью стадии households.</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="D18" s="28" t="inlineStr">
         <is>
-          <t>Суммарная ёмкость магистрали — 245.2 волокно-км (централизованная схема: 429.0).</t>
+          <t>Суммарная ёмкость магистрали — 248.0 волокно-км (централизованная схема: 432.4).</t>
         </is>
       </c>
     </row>

--- a/download/Топольное_тест/BoQ_FTTH_Топольное_тест_генерализации.xlsx
+++ b/download/Топольное_тест/BoQ_FTTH_Топольное_тест_генерализации.xlsx
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="F7" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G7" s="12">
         <f>SUM(F7:F7)</f>
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="F8" s="7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G8" s="8">
         <f>SUM(F8:F8)</f>
@@ -737,7 +737,7 @@
         </is>
       </c>
       <c r="F9" s="11" t="n">
-        <v>270</v>
+        <v>213</v>
       </c>
       <c r="G9" s="12">
         <f>SUM(F9:F9)</f>
@@ -764,7 +764,7 @@
         </is>
       </c>
       <c r="F10" s="7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G10" s="8">
         <f>SUM(F10:F10)</f>
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="G12" s="14">
         <f>SUM(F12:F12)</f>
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="F13" s="15" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="G13" s="16">
         <f>SUM(F13:F13)</f>
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="G14" s="14">
         <f>SUM(F14:F14)</f>
@@ -884,7 +884,7 @@
         </is>
       </c>
       <c r="F15" s="15" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="G15" s="16">
         <f>SUM(F15:F15)</f>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G16" s="14">
         <f>SUM(F16:F16)</f>
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="F17" s="15" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="G17" s="16">
         <f>SUM(F17:F17)</f>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="G18" s="14">
         <f>SUM(F18:F18)</f>
@@ -991,9 +991,7 @@
           <t>волокна участка = 1,25 × ДХ потока</t>
         </is>
       </c>
-      <c r="F19" s="15" t="n">
-        <v>0.2</v>
-      </c>
+      <c r="F19" s="15" t="n"/>
       <c r="G19" s="16">
         <f>SUM(F19:F19)</f>
         <v/>
@@ -1019,7 +1017,7 @@
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="G20" s="14">
         <f>SUM(F20:F20)</f>
@@ -1046,7 +1044,7 @@
         </is>
       </c>
       <c r="F21" s="15" t="n">
-        <v>12.2</v>
+        <v>8.9</v>
       </c>
       <c r="G21" s="16">
         <f>SUM(F21:F21)</f>
@@ -1073,7 +1071,7 @@
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>248</v>
+        <v>182.3</v>
       </c>
       <c r="G22" s="14">
         <f>SUM(F22:F22)</f>
@@ -1112,7 +1110,7 @@
         </is>
       </c>
       <c r="F24" s="7" t="n">
-        <v>160</v>
+        <v>127</v>
       </c>
       <c r="G24" s="8">
         <f>SUM(F24:F24)</f>
@@ -1151,7 +1149,7 @@
         </is>
       </c>
       <c r="F26" s="7" t="n">
-        <v>258</v>
+        <v>205</v>
       </c>
       <c r="G26" s="8">
         <f>SUM(F26:F26)</f>
@@ -1178,7 +1176,7 @@
         </is>
       </c>
       <c r="F27" s="11" t="n">
-        <v>284</v>
+        <v>226</v>
       </c>
       <c r="G27" s="12">
         <f>SUM(F27:F27)</f>
@@ -1205,7 +1203,7 @@
         </is>
       </c>
       <c r="F28" s="7" t="n">
-        <v>581</v>
+        <v>460</v>
       </c>
       <c r="G28" s="8">
         <f>SUM(F28:F28)</f>
@@ -1232,7 +1230,7 @@
         </is>
       </c>
       <c r="F29" s="11" t="n">
-        <v>581</v>
+        <v>460</v>
       </c>
       <c r="G29" s="12">
         <f>SUM(F29:F29)</f>
@@ -1259,7 +1257,7 @@
         </is>
       </c>
       <c r="F30" s="7" t="n">
-        <v>421</v>
+        <v>346</v>
       </c>
       <c r="G30" s="8">
         <f>SUM(F30:F30)</f>
@@ -1286,7 +1284,7 @@
         </is>
       </c>
       <c r="F31" s="11" t="n">
-        <v>516</v>
+        <v>410</v>
       </c>
       <c r="G31" s="12">
         <f>SUM(F31:F31)</f>
@@ -1313,7 +1311,7 @@
         </is>
       </c>
       <c r="F32" s="7" t="n">
-        <v>1548</v>
+        <v>1230</v>
       </c>
       <c r="G32" s="8">
         <f>SUM(F32:F32)</f>
@@ -1501,44 +1499,44 @@
       </c>
       <c r="E5" s="17" t="n"/>
       <c r="F5" s="7" t="n">
-        <v>258</v>
+        <v>205</v>
       </c>
       <c r="G5" s="7">
         <f>IFERROR(F5/E5-1,"")</f>
         <v/>
       </c>
       <c r="H5" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>160</v>
+        <v>127</v>
       </c>
       <c r="J5" s="7" t="n">
-        <v>14.03</v>
+        <v>11.45</v>
       </c>
       <c r="K5" s="19" t="n">
-        <v>11.52</v>
+        <v>8.43</v>
       </c>
       <c r="L5" s="19" t="n">
-        <v>44.7</v>
+        <v>41.1</v>
       </c>
       <c r="M5" s="7" t="n">
-        <v>98.8</v>
+        <v>109.2</v>
       </c>
       <c r="N5" s="7" t="n">
-        <v>248</v>
+        <v>182.3</v>
       </c>
       <c r="O5" s="7" t="n">
-        <v>432.4</v>
+        <v>260.4</v>
       </c>
       <c r="P5" s="7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q5" s="7" t="n">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="R5" s="7" t="n">
-        <v>543.4</v>
+        <v>491.9</v>
       </c>
     </row>
     <row r="6" ht="26" customHeight="1">
@@ -1675,10 +1673,10 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>258</v>
+        <v>205</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>258</v>
+        <v>205</v>
       </c>
       <c r="E5" s="25">
         <f>IFERROR(D5/C5-1,"")</f>
@@ -1695,7 +1693,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E6" s="26">
         <f>IFERROR(D6/C6-1,"")</f>
@@ -1709,10 +1707,10 @@
         </is>
       </c>
       <c r="C7" s="13" t="n">
-        <v>432.4</v>
+        <v>260.4</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>248</v>
+        <v>182.3</v>
       </c>
       <c r="E7" s="13">
         <f>IFERROR(D7/C7-1,"")</f>
@@ -1726,10 +1724,10 @@
         </is>
       </c>
       <c r="C8" s="15" t="n">
-        <v>16.5</v>
+        <v>12.8</v>
       </c>
       <c r="D8" s="15" t="n">
-        <v>15.43</v>
+        <v>12.67</v>
       </c>
       <c r="E8" s="15">
         <f>IFERROR(D8/C8-1,"")</f>
@@ -1743,10 +1741,10 @@
         </is>
       </c>
       <c r="C9" s="13" t="n">
-        <v>12.2</v>
+        <v>8.9</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>12.2</v>
+        <v>8.9</v>
       </c>
       <c r="E9" s="13">
         <f>IFERROR(D9/C9-1,"")</f>
@@ -1760,10 +1758,10 @@
         </is>
       </c>
       <c r="C10" s="15" t="n">
-        <v>28.7</v>
+        <v>21.7</v>
       </c>
       <c r="D10" s="15" t="n">
-        <v>27.6</v>
+        <v>21.6</v>
       </c>
       <c r="E10" s="15">
         <f>IFERROR(D10/C10-1,"")</f>
@@ -1777,10 +1775,10 @@
         </is>
       </c>
       <c r="C11" s="7" t="n">
-        <v>163</v>
+        <v>129</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>160</v>
+        <v>127</v>
       </c>
       <c r="E11" s="25">
         <f>IFERROR(D11/C11-1,"")</f>
@@ -1794,10 +1792,10 @@
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E12" s="26">
         <f>IFERROR(D12/C12-1,"")</f>
@@ -1811,10 +1809,10 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>568</v>
+        <v>451</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>581</v>
+        <v>460</v>
       </c>
       <c r="E13" s="25">
         <f>IFERROR(D13/C13-1,"")</f>
@@ -1831,7 +1829,7 @@
         <v>288</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>432</v>
+        <v>336</v>
       </c>
       <c r="E14" s="26">
         <f>IFERROR(D14/C14-1,"")</f>
@@ -1951,7 +1949,7 @@
       </c>
       <c r="D8" s="28" t="inlineStr">
         <is>
-          <t>258 ДХ. Отклонения от данных заказа связаны с покрытием дорог OSM и фактической застройкой; при больших расхождениях проверьте домохозяйства по превью стадии households.</t>
+          <t>205 ДХ. Отклонения от данных заказа связаны с покрытием дорог OSM и фактической застройкой; при больших расхождениях проверьте домохозяйства по превью стадии households.</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2087,7 @@
       </c>
       <c r="D18" s="28" t="inlineStr">
         <is>
-          <t>Суммарная ёмкость магистрали — 248.0 волокно-км (централизованная схема: 432.4).</t>
+          <t>Суммарная ёмкость магистрали — 182.3 волокно-км (централизованная схема: 260.4).</t>
         </is>
       </c>
     </row>

--- a/download/Топольное_тест/BoQ_FTTH_Топольное_тест_генерализации.xlsx
+++ b/download/Топольное_тест/BoQ_FTTH_Топольное_тест_генерализации.xlsx
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
       <c r="G12" s="14">
         <f>SUM(F12:F12)</f>
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="F13" s="15" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="G13" s="16">
         <f>SUM(F13:F13)</f>
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="G14" s="14">
         <f>SUM(F14:F14)</f>
@@ -884,7 +884,7 @@
         </is>
       </c>
       <c r="F15" s="15" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="G15" s="16">
         <f>SUM(F15:F15)</f>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G16" s="14">
         <f>SUM(F16:F16)</f>
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="F17" s="15" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="G17" s="16">
         <f>SUM(F17:F17)</f>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="G18" s="14">
         <f>SUM(F18:F18)</f>
@@ -1016,9 +1016,7 @@
           <t>волокна участка = 1,25 × ДХ потока</t>
         </is>
       </c>
-      <c r="F20" s="13" t="n">
-        <v>0.2</v>
-      </c>
+      <c r="F20" s="13" t="n"/>
       <c r="G20" s="14">
         <f>SUM(F20:F20)</f>
         <v/>
@@ -1044,7 +1042,7 @@
         </is>
       </c>
       <c r="F21" s="15" t="n">
-        <v>8.9</v>
+        <v>8.5</v>
       </c>
       <c r="G21" s="16">
         <f>SUM(F21:F21)</f>
@@ -1071,7 +1069,7 @@
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>182.3</v>
+        <v>188.1</v>
       </c>
       <c r="G22" s="14">
         <f>SUM(F22:F22)</f>
@@ -1110,7 +1108,7 @@
         </is>
       </c>
       <c r="F24" s="7" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G24" s="8">
         <f>SUM(F24:F24)</f>
@@ -1257,7 +1255,7 @@
         </is>
       </c>
       <c r="F30" s="7" t="n">
-        <v>346</v>
+        <v>366</v>
       </c>
       <c r="G30" s="8">
         <f>SUM(F30:F30)</f>
@@ -1509,34 +1507,34 @@
         <v>2</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="J5" s="7" t="n">
-        <v>11.45</v>
+        <v>12.18</v>
       </c>
       <c r="K5" s="19" t="n">
-        <v>8.43</v>
+        <v>8.01</v>
       </c>
       <c r="L5" s="19" t="n">
-        <v>41.1</v>
+        <v>39.1</v>
       </c>
       <c r="M5" s="7" t="n">
         <v>109.2</v>
       </c>
       <c r="N5" s="7" t="n">
-        <v>182.3</v>
+        <v>188.1</v>
       </c>
       <c r="O5" s="7" t="n">
-        <v>260.4</v>
+        <v>247</v>
       </c>
       <c r="P5" s="7" t="n">
         <v>4</v>
       </c>
       <c r="Q5" s="7" t="n">
-        <v>103</v>
+        <v>54</v>
       </c>
       <c r="R5" s="7" t="n">
-        <v>491.9</v>
+        <v>501.7</v>
       </c>
     </row>
     <row r="6" ht="26" customHeight="1">
@@ -1707,10 +1705,10 @@
         </is>
       </c>
       <c r="C7" s="13" t="n">
-        <v>260.4</v>
+        <v>247</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>182.3</v>
+        <v>188.1</v>
       </c>
       <c r="E7" s="13">
         <f>IFERROR(D7/C7-1,"")</f>
@@ -1724,10 +1722,10 @@
         </is>
       </c>
       <c r="C8" s="15" t="n">
-        <v>12.8</v>
+        <v>13.8</v>
       </c>
       <c r="D8" s="15" t="n">
-        <v>12.67</v>
+        <v>13.4</v>
       </c>
       <c r="E8" s="15">
         <f>IFERROR(D8/C8-1,"")</f>
@@ -1741,10 +1739,10 @@
         </is>
       </c>
       <c r="C9" s="13" t="n">
-        <v>8.9</v>
+        <v>8.5</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>8.9</v>
+        <v>8.5</v>
       </c>
       <c r="E9" s="13">
         <f>IFERROR(D9/C9-1,"")</f>
@@ -1758,10 +1756,10 @@
         </is>
       </c>
       <c r="C10" s="15" t="n">
-        <v>21.7</v>
+        <v>22.3</v>
       </c>
       <c r="D10" s="15" t="n">
-        <v>21.6</v>
+        <v>21.9</v>
       </c>
       <c r="E10" s="15">
         <f>IFERROR(D10/C10-1,"")</f>
@@ -1775,10 +1773,10 @@
         </is>
       </c>
       <c r="C11" s="7" t="n">
+        <v>131</v>
+      </c>
+      <c r="D11" s="7" t="n">
         <v>129</v>
-      </c>
-      <c r="D11" s="7" t="n">
-        <v>127</v>
       </c>
       <c r="E11" s="25">
         <f>IFERROR(D11/C11-1,"")</f>
@@ -1829,7 +1827,7 @@
         <v>288</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>336</v>
+        <v>384</v>
       </c>
       <c r="E14" s="26">
         <f>IFERROR(D14/C14-1,"")</f>
@@ -2087,7 +2085,7 @@
       </c>
       <c r="D18" s="28" t="inlineStr">
         <is>
-          <t>Суммарная ёмкость магистрали — 182.3 волокно-км (централизованная схема: 260.4).</t>
+          <t>Суммарная ёмкость магистрали — 188.1 волокно-км (централизованная схема: 247.0).</t>
         </is>
       </c>
     </row>
